--- a/data/trans_orig/IP07A09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A09-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>21540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15758</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26833</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>29600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>37689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53561</t>
+          <t>53323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12165</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24877</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37623</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18091</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20491</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16847</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>21826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31405</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>35926</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50656</t>
+          <t>50845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27155</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42572</t>
+          <t>43623</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26757</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35420</t>
+          <t>34770</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58610</t>
+          <t>57595</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37394</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52854</t>
+          <t>52876</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59804</t>
+          <t>58546</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>84941</t>
+          <t>85953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106368</t>
+          <t>107489</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>34699</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22846</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23207</t>
+          <t>22924</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>37789</t>
+          <t>38748</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34247</t>
+          <t>34628</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>29750</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42736</t>
+          <t>43299</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55842</t>
+          <t>55632</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73207</t>
+          <t>74339</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22695</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>42564</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>56307</t>
+          <t>55934</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,04%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,82 +4839,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>7396</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>13165</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>3222</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>7683</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>7396</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>3952</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>13759</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13015</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>46543</t>
+          <t>44999</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>67712</t>
+          <t>67087</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>43744</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>64854</t>
+          <t>64877</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>94433</t>
+          <t>94338</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>127546</t>
+          <t>125455</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>63405</t>
+          <t>62693</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>86343</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>75905</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>100065</t>
+          <t>100915</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>145044</t>
+          <t>143216</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>179744</t>
+          <t>181124</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>139042</t>
+          <t>137847</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>165946</t>
+          <t>166499</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>163815</t>
+          <t>163826</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>191143</t>
+          <t>191633</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>312176</t>
+          <t>311928</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>351733</t>
+          <t>351267</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>17212</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28674</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16307</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26528</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>20975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20624</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38582</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21827</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>15169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40575</t>
+          <t>40352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17149</t>
+          <t>17363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30151</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27662</t>
+          <t>27045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29299</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42865</t>
+          <t>43174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>29422</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35355</t>
+          <t>33829</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54641</t>
+          <t>54322</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42799</t>
+          <t>43520</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40273</t>
+          <t>40094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>55654</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44561</t>
+          <t>45291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>61651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90260</t>
+          <t>90828</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113291</t>
+          <t>112200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22530</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35507</t>
+          <t>35904</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>28998</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>45302</t>
+          <t>45963</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>30716</t>
+          <t>30785</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45067</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>31582</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45038</t>
+          <t>44533</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65355</t>
+          <t>65264</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85472</t>
+          <t>85656</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28640</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>30526</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>43553</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19932</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>47639</t>
+          <t>48064</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>70003</t>
+          <t>70927</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>54980</t>
+          <t>54906</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>78633</t>
+          <t>78308</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>108676</t>
+          <t>108206</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>142772</t>
+          <t>141428</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>66760</t>
+          <t>67619</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>92953</t>
+          <t>91963</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>54412</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>78056</t>
+          <t>77033</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>128206</t>
+          <t>128157</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>162440</t>
+          <t>161570</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>135845</t>
+          <t>135657</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>165343</t>
+          <t>164641</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>150616</t>
+          <t>152001</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>180121</t>
+          <t>179694</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>296255</t>
+          <t>294296</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>337113</t>
+          <t>335344</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17347</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30267</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22148</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36793</t>
+          <t>36695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,39 +11558,39 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3328</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>32475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21789</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,82 +11784,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11777</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17531</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>24,31%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>36,19%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>27568</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>20280</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>35929</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>27,32%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>20,1%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11777</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7218</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17318</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,31%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>27568</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>19979</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>34689</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30773</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36097</t>
+          <t>35631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52388</t>
+          <t>51831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>28480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>42792</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>831</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23808</t>
+          <t>24071</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28870</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49039</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24590</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40566</t>
+          <t>40795</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32250</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67519</t>
+          <t>68006</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>48749</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67869</t>
+          <t>66101</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43697</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59708</t>
+          <t>59753</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>97719</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122036</t>
+          <t>122818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,17%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21851</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>20869</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36522</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25734</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27815</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>31141</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>49406</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>28918</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43319</t>
+          <t>43245</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41669</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>60329</t>
+          <t>60238</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>80989</t>
+          <t>79783</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>28311</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14292</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>24241</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>27479</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>41118</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23756</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>32983</t>
+          <t>33976</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>52196</t>
+          <t>52338</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>75975</t>
+          <t>75287</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>57909</t>
+          <t>58273</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>82212</t>
+          <t>83869</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>115935</t>
+          <t>116406</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>150956</t>
+          <t>150880</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>85687</t>
+          <t>85919</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>113351</t>
+          <t>114150</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>75365</t>
+          <t>75798</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>102012</t>
+          <t>102310</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>166776</t>
+          <t>166917</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>205911</t>
+          <t>207451</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>139991</t>
+          <t>139052</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>169380</t>
+          <t>167673</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>154205</t>
+          <t>152079</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>184398</t>
+          <t>183503</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>300190</t>
+          <t>301196</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>345745</t>
+          <t>344037</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
